--- a/artfynd/A 55948-2025 artfynd.xlsx
+++ b/artfynd/A 55948-2025 artfynd.xlsx
@@ -1208,7 +1208,7 @@
         <v>129224234</v>
       </c>
       <c r="B7" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55948-2025 artfynd.xlsx
+++ b/artfynd/A 55948-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129000706</v>
+        <v>129000707</v>
       </c>
       <c r="B2" t="n">
-        <v>92873</v>
+        <v>90932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>841795</v>
+        <v>841774</v>
       </c>
       <c r="R2" t="n">
-        <v>7448526</v>
+        <v>7448557</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000707</v>
+        <v>129000709</v>
       </c>
       <c r="B3" t="n">
-        <v>90585</v>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>841774</v>
+        <v>841722</v>
       </c>
       <c r="R3" t="n">
-        <v>7448557</v>
+        <v>7448701</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000710</v>
+        <v>129000706</v>
       </c>
       <c r="B4" t="n">
-        <v>78801</v>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>841708</v>
+        <v>841795</v>
       </c>
       <c r="R4" t="n">
-        <v>7448792</v>
+        <v>7448526</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000708</v>
+        <v>129224234</v>
       </c>
       <c r="B5" t="n">
-        <v>78801</v>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,13 +1032,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>841723</v>
+        <v>841797</v>
       </c>
       <c r="R5" t="n">
-        <v>7448698</v>
+        <v>7448513</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000709</v>
+        <v>129000708</v>
       </c>
       <c r="B6" t="n">
-        <v>90585</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>841722</v>
+        <v>841723</v>
       </c>
       <c r="R6" t="n">
-        <v>7448701</v>
+        <v>7448698</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129224234</v>
+        <v>129000710</v>
       </c>
       <c r="B7" t="n">
-        <v>92901</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>841797</v>
+        <v>841708</v>
       </c>
       <c r="R7" t="n">
-        <v>7448513</v>
+        <v>7448792</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 55948-2025 artfynd.xlsx
+++ b/artfynd/A 55948-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000707</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000709</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000706</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224234</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000708</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,8 +1338,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000710</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>